--- a/data/trans_bre/P1428-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1428-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,26</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>233,49%</t>
+          <t>234,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 16,24</t>
+          <t>9,55; 15,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,76</t>
+          <t>4,39; 10,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,71</t>
+          <t>4,62; 11,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,5; 15,9</t>
+          <t>10,27; 15,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>123,71; 319,7</t>
+          <t>125,27; 315,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,48; 229,73</t>
+          <t>61,81; 239,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,47; 313,27</t>
+          <t>82,87; 329,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>146,0; 346,38</t>
+          <t>149,48; 348,21</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>8,86</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>272,83%</t>
+          <t>196,14%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,45</t>
+          <t>6,32; 12,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,35</t>
+          <t>3,37; 8,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,77</t>
+          <t>5,06; 9,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 12,3</t>
+          <t>6,78; 10,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,33; 195,03</t>
+          <t>69,1; 193,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,71; 161,48</t>
+          <t>40,45; 166,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>114,15; 373,6</t>
+          <t>114,07; 373,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>158,91; 605,17</t>
+          <t>121,74; 303,11</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,92</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>472,21%</t>
+          <t>115,05%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 14,24</t>
+          <t>7,48; 14,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,44</t>
+          <t>4,34; 9,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,19</t>
+          <t>1,54; 6,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 59,36</t>
+          <t>3,42; 8,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,05; 259,59</t>
+          <t>88,46; 261,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>97,18; 397,67</t>
+          <t>87,94; 370,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,09; 202,59</t>
+          <t>24,48; 214,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,47; 1353,19</t>
+          <t>52,16; 215,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,57</t>
+          <t>9,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>137,58%</t>
+          <t>153,14%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 12,21</t>
+          <t>6,65; 12,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,7</t>
+          <t>5,74; 10,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,97</t>
+          <t>2,61; 6,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,21</t>
+          <t>7,15; 11,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,27; 187,72</t>
+          <t>76,03; 190,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,09; 307,42</t>
+          <t>97,14; 301,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,01; 311,88</t>
+          <t>65,79; 288,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>72,62; 213,72</t>
+          <t>100,25; 239,24</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>280,35%</t>
+          <t>173,83%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,96</t>
+          <t>8,87; 12,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,63</t>
+          <t>5,94; 8,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,99</t>
+          <t>4,65; 7,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 30,46</t>
+          <t>8,03; 10,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>114,3; 185,56</t>
+          <t>112,27; 182,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>101,08; 188,81</t>
+          <t>101,4; 191,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>112,28; 221,45</t>
+          <t>112,97; 224,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>165,41; 597,11</t>
+          <t>138,57; 214,2</t>
         </is>
       </c>
     </row>
